--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T08:14:05+00:00</t>
+    <t>2025-05-27T14:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5610,7 +5610,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>219</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>482</v>
       </c>
@@ -16396,7 +16396,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>523</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
         <v>622</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>628</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>651</v>
       </c>
@@ -20386,7 +20386,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>660</v>
       </c>
@@ -24497,12 +24497,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO183">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T12:29:55+00:00</t>
+    <t>2025-10-13T08:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T08:32:48+00:00</t>
+    <t>2025-10-21T08:19:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:19:27+00:00</t>
+    <t>2025-10-21T12:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
